--- a/测试结果.xlsx
+++ b/测试结果.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4240" yWindow="640" windowWidth="28040" windowHeight="15800" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
@@ -437,6 +437,50 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>19050</colOff>
+      <row>0</row>
+      <rowOff>19050</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>38100</colOff>
+      <row>1</row>
+      <rowOff>247650</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 2" descr="szsRTU"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="0"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData fLocksWithSheet="0" fPrintsWithSheet="1"/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -865,7 +909,11 @@
           <t>TF-002</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr"/>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>登录</t>
+        </is>
+      </c>
       <c r="C3" s="23" t="inlineStr">
         <is>
           <t>教师登录成功</t>
@@ -911,7 +959,11 @@
           <t>TF-003</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr"/>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>登录</t>
+        </is>
+      </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
           <t>角色化首页区分</t>
@@ -934,7 +986,7 @@
       </c>
       <c r="G4" s="23" t="inlineStr">
         <is>
-          <t>学生首页与教师首页均 200，渲染内容不同（4891 / 4361 字节，含不同模块入口）</t>
+          <t>学生首页与教师首页均 200，渲染内容不同（4893 / 5319 字节，含不同模块入口）</t>
         </is>
       </c>
       <c r="H4" s="23" t="inlineStr"/>
@@ -957,7 +1009,11 @@
           <t>TF-004</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr"/>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>登录</t>
+        </is>
+      </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
           <t>用户名或密码错误</t>
@@ -1003,7 +1059,11 @@
           <t>TF-005</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr"/>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>登录</t>
+        </is>
+      </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
           <t>账号不存在</t>
@@ -1049,7 +1109,11 @@
           <t>TF-006</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr"/>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>登录</t>
+        </is>
+      </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
           <t>输入为空登录</t>
@@ -1095,7 +1159,11 @@
           <t>TF-007</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr"/>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>登录</t>
+        </is>
+      </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
           <t>角色权限校验</t>
@@ -1168,7 +1236,7 @@
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>注册 302 跳转登录页，新账号 stu_new_12088551 可登录：True</t>
+          <t>注册 302 跳转登录页，新账号 stu_new_53976367 可登录：True</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr"/>
@@ -1191,7 +1259,11 @@
           <t>TF-009</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr"/>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
           <t>用户名重复注册</t>
@@ -1237,7 +1309,11 @@
           <t>TF-010</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr"/>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
           <t>密码与确认密码不一致</t>
@@ -1283,7 +1359,11 @@
           <t>TF-011</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr"/>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
           <t>密码长度不符合要求</t>
@@ -1329,7 +1409,11 @@
           <t>TF-012</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr"/>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
           <t>必填项为空注册</t>
@@ -1375,7 +1459,11 @@
           <t>TF-013</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr"/>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
           <t>非法字符注册</t>
@@ -1471,7 +1559,11 @@
           <t>TF-015</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr"/>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>题目新增</t>
+        </is>
+      </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
           <t>必填字段缺失</t>
@@ -1517,7 +1609,11 @@
           <t>TF-016</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr"/>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>题目新增</t>
+        </is>
+      </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
           <t>无测试用例创建</t>
@@ -1563,7 +1659,11 @@
           <t>TF-017</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr"/>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>题目新增</t>
+        </is>
+      </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
           <t>新题目可检索</t>
@@ -1609,7 +1709,11 @@
           <t>TF-018</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr"/>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>题目新增</t>
+        </is>
+      </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
           <t>学生新增题目</t>
@@ -1705,7 +1809,11 @@
           <t>TF-020</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr"/>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>题目删除</t>
+        </is>
+      </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
           <t>删除他人题目</t>
@@ -1751,7 +1859,11 @@
           <t>TF-021</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr"/>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>题目删除</t>
+        </is>
+      </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
           <t>删除不存在的题目</t>
@@ -1797,7 +1909,11 @@
           <t>TF-022</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr"/>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>题目删除</t>
+        </is>
+      </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
           <t>学生删除题目</t>
@@ -1893,7 +2009,11 @@
           <t>TF-024</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr"/>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>题目查询</t>
+        </is>
+      </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
           <t>按知识点筛选</t>
@@ -1939,7 +2059,11 @@
           <t>TF-025</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr"/>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>题目查询</t>
+        </is>
+      </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
           <t>按难度筛选</t>
@@ -1985,7 +2109,11 @@
           <t>TF-026</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr"/>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>题目查询</t>
+        </is>
+      </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
           <t>查询无结果</t>
@@ -2031,7 +2159,11 @@
           <t>TF-027</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr"/>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>题目查询</t>
+        </is>
+      </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
           <t>题目详情</t>
@@ -2127,7 +2259,11 @@
           <t>TF-029</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr"/>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>题目修改</t>
+        </is>
+      </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
           <t>修改用例影响判题</t>
@@ -2173,7 +2309,11 @@
           <t>TF-030</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr"/>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>题目修改</t>
+        </is>
+      </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
           <t>修改为非法数据</t>
@@ -2219,7 +2359,11 @@
           <t>TF-031</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr"/>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>题目修改</t>
+        </is>
+      </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
           <t>学生修改题目</t>
@@ -2292,7 +2436,7 @@
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>正确代码判题返回 AC，生成提交记录（id=60）</t>
+          <t>正确代码判题返回 AC，生成提交记录（id=129）</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr"/>
@@ -2315,7 +2459,11 @@
           <t>TF-033</t>
         </is>
       </c>
-      <c r="B34" s="23" t="inlineStr"/>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>判题提交</t>
+        </is>
+      </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
           <t>错误答案判题 WA</t>
@@ -2361,7 +2509,11 @@
           <t>TF-034</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr"/>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>判题提交</t>
+        </is>
+      </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
           <t>语法错误判题 CE</t>
@@ -2407,7 +2559,11 @@
           <t>TF-035</t>
         </is>
       </c>
-      <c r="B36" s="23" t="inlineStr"/>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>判题提交</t>
+        </is>
+      </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
           <t>死循环判题 TLE</t>
@@ -2430,7 +2586,7 @@
       </c>
       <c r="G36" s="23" t="inlineStr">
         <is>
-          <t>死循环被时间限制中断，返回 TLE，未挂起（用时约 6.0s）</t>
+          <t>死循环被时间限制中断，返回 TLE，未挂起（用时约 6.1s）</t>
         </is>
       </c>
       <c r="H36" s="23" t="inlineStr"/>
@@ -2453,7 +2609,11 @@
           <t>TF-036</t>
         </is>
       </c>
-      <c r="B37" s="23" t="inlineStr"/>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>判题提交</t>
+        </is>
+      </c>
       <c r="C37" s="23" t="inlineStr">
         <is>
           <t>禁用模块判题 RE</t>
@@ -2499,7 +2659,11 @@
           <t>TF-037</t>
         </is>
       </c>
-      <c r="B38" s="23" t="inlineStr"/>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>判题提交</t>
+        </is>
+      </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
           <t>超长代码限制</t>
@@ -2572,7 +2736,7 @@
       </c>
       <c r="G39" s="23" t="inlineStr">
         <is>
-          <t>提交记录列表 200，AC 筛选生效并可见本次提交（id=60）</t>
+          <t>提交记录列表 200，AC 筛选生效并可见本次提交（id=129）</t>
         </is>
       </c>
       <c r="H39" s="23" t="inlineStr"/>
@@ -2595,7 +2759,11 @@
           <t>TF-039</t>
         </is>
       </c>
-      <c r="B40" s="23" t="inlineStr"/>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>提交记录</t>
+        </is>
+      </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
           <t>未登录访问拦截</t>
@@ -2641,7 +2809,11 @@
           <t>TF-040</t>
         </is>
       </c>
-      <c r="B41" s="23" t="inlineStr"/>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>提交记录</t>
+        </is>
+      </c>
       <c r="C41" s="23" t="inlineStr">
         <is>
           <t>提交记录分页</t>
@@ -2664,7 +2836,7 @@
       </c>
       <c r="G41" s="23" t="inlineStr">
         <is>
-          <t>第 2 页与第 1 页内容不同，翻页正常（48 条提交，每页 15 条）</t>
+          <t>第 2 页与第 1 页内容不同，翻页正常（109 条提交，每页 15 条）</t>
         </is>
       </c>
       <c r="H41" s="23" t="inlineStr"/>
@@ -2687,7 +2859,11 @@
           <t>TF-041</t>
         </is>
       </c>
-      <c r="B42" s="23" t="inlineStr"/>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>提交记录</t>
+        </is>
+      </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
           <t>学生查看他人提交</t>
@@ -2733,7 +2909,11 @@
           <t>TF-042</t>
         </is>
       </c>
-      <c r="B43" s="23" t="inlineStr"/>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>提交记录</t>
+        </is>
+      </c>
       <c r="C43" s="23" t="inlineStr">
         <is>
           <t>教师查看本班学生提交</t>
@@ -2779,7 +2959,11 @@
           <t>TF-043</t>
         </is>
       </c>
-      <c r="B44" s="23" t="inlineStr"/>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>提交记录</t>
+        </is>
+      </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
           <t>非本班教师查看提交</t>
@@ -2875,7 +3059,11 @@
           <t>TF-045</t>
         </is>
       </c>
-      <c r="B46" s="23" t="inlineStr"/>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>作业提交</t>
+        </is>
+      </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
           <t>学生提交非本班作业</t>
@@ -3071,7 +3259,11 @@
           <t>TF-049</t>
         </is>
       </c>
-      <c r="B50" s="23" t="inlineStr"/>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
       <c r="C50" s="23" t="inlineStr">
         <is>
           <t>用户管理列表加载</t>
@@ -3117,7 +3309,11 @@
           <t>TF-050</t>
         </is>
       </c>
-      <c r="B51" s="23" t="inlineStr"/>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
       <c r="C51" s="23" t="inlineStr">
         <is>
           <t>管理员新增教师账号</t>
@@ -3163,7 +3359,11 @@
           <t>TF-051</t>
         </is>
       </c>
-      <c r="B52" s="23" t="inlineStr"/>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
       <c r="C52" s="23" t="inlineStr">
         <is>
           <t>管理员编辑账号信息</t>
@@ -3209,7 +3409,11 @@
           <t>TF-052</t>
         </is>
       </c>
-      <c r="B53" s="23" t="inlineStr"/>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
       <c r="C53" s="23" t="inlineStr">
         <is>
           <t>管理员重置密码</t>
@@ -3255,7 +3459,11 @@
           <t>TF-053</t>
         </is>
       </c>
-      <c r="B54" s="23" t="inlineStr"/>
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
       <c r="C54" s="23" t="inlineStr">
         <is>
           <t>管理员停用账号</t>
@@ -3301,7 +3509,11 @@
           <t>TF-054</t>
         </is>
       </c>
-      <c r="B55" s="23" t="inlineStr"/>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
       <c r="C55" s="23" t="inlineStr">
         <is>
           <t>管理员删除账号</t>
@@ -3347,7 +3559,11 @@
           <t>TF-055</t>
         </is>
       </c>
-      <c r="B56" s="23" t="inlineStr"/>
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
       <c r="C56" s="23" t="inlineStr">
         <is>
           <t>非管理员访问用户管理</t>
@@ -3393,7 +3609,11 @@
           <t>TF-056</t>
         </is>
       </c>
-      <c r="B57" s="23" t="inlineStr"/>
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>管理员</t>
+        </is>
+      </c>
       <c r="C57" s="23" t="inlineStr">
         <is>
           <t>注册页无法提权为管理员</t>
@@ -3436,7 +3656,7 @@
     <row r="59">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>测试统计：共执行 56 条用例，通过 56 条、失败 0 条；执行时间 2026-10-31 23:32:20</t>
+          <t>测试统计：共执行 56 条用例，通过 56 条、失败 0 条；执行时间 2026-11-01 00:14:06</t>
         </is>
       </c>
     </row>
@@ -3534,5 +3754,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="1" scale="100"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>